--- a/docs/设计评审会议纪要模板.xlsx
+++ b/docs/设计评审会议纪要模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Workflow_Approval_System\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4827A648-ABDE-4980-94E2-10663FDA1B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA028C36-C5D9-4185-9020-3C45C9EFB91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>时间</t>
   </si>
@@ -69,6 +69,10 @@
   </si>
   <si>
     <t>{{当前日期}}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{难度}}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -284,57 +288,57 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -647,48 +651,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="26"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="28"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="19" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="10"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="13"/>
       <c r="I3" s="1" t="s">
         <v>2</v>
       </c>
@@ -699,77 +705,77 @@
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:11" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="26"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" spans="1:11" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="28"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="13"/>
       <c r="K8" s="1" t="s">
         <v>9</v>
       </c>
@@ -778,44 +784,44 @@
       <c r="A9" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="13"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>3</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="13"/>
       <c r="J11" s="5"/>
       <c r="K11" s="2"/>
     </row>
@@ -823,14 +829,14 @@
       <c r="A12" s="1">
         <v>4</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
       <c r="J12" s="5"/>
       <c r="K12" s="2"/>
     </row>
@@ -838,14 +844,14 @@
       <c r="A13" s="1">
         <v>5</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="11"/>
       <c r="J13" s="5"/>
       <c r="K13" s="2"/>
     </row>
@@ -853,14 +859,14 @@
       <c r="A14" s="1">
         <v>6</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="5"/>
       <c r="K14" s="2"/>
     </row>
@@ -868,29 +874,29 @@
       <c r="A15" s="1">
         <v>7</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="13"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>8</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="13"/>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -898,14 +904,14 @@
       <c r="A17" s="1">
         <v>9</v>
       </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="13"/>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
@@ -913,14 +919,14 @@
       <c r="A18" s="1">
         <v>10</v>
       </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
       <c r="J18" s="6"/>
       <c r="K18" s="2"/>
     </row>
@@ -928,14 +934,14 @@
       <c r="A19" s="1">
         <v>11</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="13"/>
       <c r="J19" s="6"/>
       <c r="K19" s="2"/>
     </row>
@@ -943,14 +949,14 @@
       <c r="A20" s="1">
         <v>12</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="13"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
     </row>
@@ -958,14 +964,14 @@
       <c r="A21" s="1">
         <v>13</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="13"/>
       <c r="J21" s="6"/>
       <c r="K21" s="3"/>
     </row>
@@ -973,23 +979,35 @@
       <c r="A22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="10"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="13"/>
       <c r="D22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="10"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="13"/>
       <c r="G22" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="10"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B10:J10"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="B15:J15"/>
@@ -1003,18 +1021,6 @@
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B10:J10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="E22:F22"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.39370078740157499" right="0.39370078740157499" top="0.59055118110236204" bottom="0.59055118110236204" header="0.31496062992126" footer="0.31496062992126"/>
